--- a/docs/Risikomanagement/Risikomanagement.xlsx
+++ b/docs/Risikomanagement/Risikomanagement.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siemens-my.sharepoint.com/personal/johannes_opitz_siemens_com/Documents/Theoriephasen/Semester 3/Softwareentwicklung/DualNetProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71915484-DD4D-4726-B2AC-EAE013EB423A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68975E4C-BA2E-4158-A9DD-7D5BDC8BEA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{245C3D26-10D1-4C11-B897-19ECAFC65862}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="100">
   <si>
     <t>Risikomanagement</t>
   </si>
@@ -48,24 +48,6 @@
   </si>
   <si>
     <t>Beschreibung</t>
-  </si>
-  <si>
-    <t>Minimierungs - Strategien</t>
-  </si>
-  <si>
-    <t>Indikatoren</t>
-  </si>
-  <si>
-    <t>Notfallplan</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Verantwortlicher</t>
-  </si>
-  <si>
-    <t>Datum der letzen Aktualisierung</t>
   </si>
   <si>
     <r>
@@ -84,106 +66,273 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Schadenshöhe *</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Risiko - Score *</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>Minimierungs - Strategien</t>
+  </si>
+  <si>
+    <t>Indikatoren</t>
+  </si>
+  <si>
+    <t>Notfallplan</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Verantwortlicher</t>
+  </si>
+  <si>
+    <t>Datum der letzen Aktualisierung</t>
+  </si>
+  <si>
     <t>R-01</t>
   </si>
   <si>
+    <t>Missverständnis der
+ Anforderungen (kleine Anforderung)</t>
+  </si>
+  <si>
+    <t>Hoch (4)</t>
+  </si>
+  <si>
+    <t>Gering (2)</t>
+  </si>
+  <si>
+    <t>Risikobereich (8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurze Absprache vor 
+Entwicklung kleinerer 
+Anforderungen mit Fokus auf Verständnis </t>
+  </si>
+  <si>
+    <t>&gt;Anzahl offener 
+Rückfragen pro Anforderung.
+&gt;Anzahl Rework-Tickets pro Feature.</t>
+  </si>
+  <si>
+    <t>Schnelle Korrektur der Fehler, 
+oder entfernen der inkorrekten Umsetzung</t>
+  </si>
+  <si>
+    <t>in Bearbeitung</t>
+  </si>
+  <si>
+    <t>Ali, Sebo, Max, 
+Johannes</t>
+  </si>
+  <si>
     <t>R-02</t>
   </si>
   <si>
+    <t>Missverständnis der
+ Anforderungen (mittlere Anforderung)</t>
+  </si>
+  <si>
+    <t>Mittel (3)</t>
+  </si>
+  <si>
+    <t>Risikobereich (9)</t>
+  </si>
+  <si>
+    <t>Genaue Ausdefinierungen 
+der mittleren Anforderungen mit Gespräch im Team und Kontrolle nach Fertigung</t>
+  </si>
+  <si>
+    <t>reduziert</t>
+  </si>
+  <si>
     <t>R-03</t>
   </si>
   <si>
+    <t>Missverständnis der
+ Anforderungen (große Anforderung)</t>
+  </si>
+  <si>
+    <t>Mittel (4)</t>
+  </si>
+  <si>
+    <t>Klare Ziele zu Beginn jeder
+ Entwicklungsphase. Klare Ausdefinierungen der einzelnen Elemente. Feedback zu Umgesetzten Features.</t>
+  </si>
+  <si>
+    <t>Problembehandlung im Team.
+Kommunikation im Team und wenn nötig Anforderungen an Umsetzung anpassen</t>
+  </si>
+  <si>
+    <t>eleminiert</t>
+  </si>
+  <si>
     <t>R-04</t>
   </si>
   <si>
+    <t>Änderungen an den
+ Anforderungen nach Projektstart</t>
+  </si>
+  <si>
+    <t>Gefahrenbereich (12)</t>
+  </si>
+  <si>
+    <t>Klare Absprachen zu Beginn 
+der einzelnen Phasen und frühzeitige Funktionsanalyse</t>
+  </si>
+  <si>
+    <t>&gt;Durchschnittliche 
+Auswirkung einer Änderung auf Zeit/Kosten</t>
+  </si>
+  <si>
+    <t>Anpassung der Anforderung in 
+Rücksprache mit dem Team oder Anpassung auf Feature</t>
+  </si>
+  <si>
+    <t>offen</t>
+  </si>
+  <si>
+    <t>Johannes</t>
+  </si>
+  <si>
     <t>R-05</t>
   </si>
   <si>
+    <t>Mangelndes Engagement 
+des Teams / Entwickler</t>
+  </si>
+  <si>
+    <t>Gegenseitiges motivieren und 
+Fokussierung auf das Ziel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt; Teilnahmequote an Meetings in %.
+&gt;  Erfüllungsquote zugesagter Tasks pro Sprint
+</t>
+  </si>
+  <si>
+    <t>Admin Rechte entziehen und 
+Aufgaben auf das restliche Team auslagern</t>
+  </si>
+  <si>
     <t>R-06</t>
   </si>
   <si>
+    <t>Fehlende Kompalibität 
+der Software zu Endgeräten</t>
+  </si>
+  <si>
+    <t>Sehr gering (1)</t>
+  </si>
+  <si>
+    <t>Akzeptanzbereich (4)</t>
+  </si>
+  <si>
+    <t>Vorab Recherge zu Soft- und 
+Hardware</t>
+  </si>
+  <si>
+    <t>&gt; Anzahl gemeldeter Kompatibilitätsfehler
+&gt; Anzahl Darstellungs- oder Funktionsfehler pro Plattform</t>
+  </si>
+  <si>
+    <t>Endgeräte Anpassen/ Andere 
+Bibliotheken etc. verwenden</t>
+  </si>
+  <si>
+    <t>Ali, Sebo</t>
+  </si>
+  <si>
     <t>R-07</t>
   </si>
   <si>
+    <t xml:space="preserve"> Unzureichende oder 
+unrealistische Zeit- und Kostenplanung (P&amp;C)</t>
+  </si>
+  <si>
+    <t>Konsequentes zusammensetzten
+und Gespräche zur aktuellen Zeitplanung. Bei defizieten Rücksprache &amp; Korrektur.</t>
+  </si>
+  <si>
+    <t>&gt; Anzahl verschobener Meilensteine
+&gt; Anteil unerledigter Aufgaben pro Sprint</t>
+  </si>
+  <si>
+    <t>Mehr Zeit anfragen/ Geplante 
+Feature anpassen</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
     <t>R-08</t>
   </si>
   <si>
+    <t>Datenmodellierung in 
+MongoDB ist ineffizient oder fehlerhaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johannes, lock in </t>
+  </si>
+  <si>
+    <t>&gt; Durchschnittliche Antwortzeit datenbankbasierter Abfragen
+&gt; Anzahl fehlerhafter oder inkonsistenter Datensätze</t>
+  </si>
+  <si>
+    <t>Neu aufsetzen (falls möglich),
+ sonst auf lokole Möglichkeiten ausweichen oder Datenmenge reduzieren</t>
+  </si>
+  <si>
     <t>R-09</t>
   </si>
   <si>
-    <t>Sehr gering (1)</t>
-  </si>
-  <si>
-    <t>Gering (2)</t>
-  </si>
-  <si>
-    <t>Mittel (3)</t>
-  </si>
-  <si>
-    <t>Hoch (4)</t>
-  </si>
-  <si>
-    <t>Sehr gering (1):</t>
-  </si>
-  <si>
-    <t>Gering (2):</t>
-  </si>
-  <si>
-    <t>Hoch (4):</t>
-  </si>
-  <si>
-    <t>Mittel (3):</t>
-  </si>
-  <si>
-    <t>Sehr hoch (5):</t>
-  </si>
-  <si>
-    <t>&lt;10%</t>
-  </si>
-  <si>
-    <t>10% - 30%</t>
-  </si>
-  <si>
-    <t>30% - 60%</t>
-  </si>
-  <si>
-    <t>60% - 90%</t>
-  </si>
-  <si>
-    <t>&gt;90%</t>
-  </si>
-  <si>
-    <t>Geringfügige Auswirkung, leicht zu beheben (z.B. kleine Bugs)</t>
-  </si>
-  <si>
-    <t>Kleinere Verzögerungen (z.B Feature muss überarbeitet werden)</t>
-  </si>
-  <si>
-    <t>Deutliche Verzögerung, moderate Kosten, Beeinträchtigung der Qualität (z.B. Teilfunktionalität muss neu entwickelt werden)</t>
-  </si>
-  <si>
-    <t>Kritische Verzögerung, hohe Kosten, Projektziele gefährdet (z.B. Systemausfall, großer Datenverlust)</t>
-  </si>
-  <si>
-    <t>Projektabbruch, schwerwiegende finanzielle/reputative Schäden</t>
-  </si>
-  <si>
-    <t>Akzeptanzbereich:</t>
-  </si>
-  <si>
-    <t>Risikobereich:</t>
-  </si>
-  <si>
-    <t>Gefahrenbereich:</t>
-  </si>
-  <si>
-    <t>1 bis 4</t>
-  </si>
-  <si>
-    <t>5 bis 9</t>
-  </si>
-  <si>
-    <t>10 bis 25</t>
+    <t>Sicherheitslücken in der 
+Web-Applikation</t>
+  </si>
+  <si>
+    <t>Hoch (5)</t>
+  </si>
+  <si>
+    <t>Gefahrenbereich (15)</t>
+  </si>
+  <si>
+    <t>Unit Tests durchführen und 
+Verschlüsselungen testen/ prüfen</t>
+  </si>
+  <si>
+    <t>&gt; Anzahl gefundener Sicherheitslücken pro Testlauf
+&gt; Zeit bis zur Behebung sicherheitsrelevanter Schwachstellen</t>
+  </si>
+  <si>
+    <t>Nicht veröffentlichen/ Features 
+mit Sicherheitsriko entfernen/ Keine Sensiblen Daten Sammeln/ Auf Lücke hinweisen</t>
   </si>
   <si>
     <r>
@@ -212,6 +361,36 @@
     </r>
   </si>
   <si>
+    <t>Sehr gering (1):</t>
+  </si>
+  <si>
+    <t>&lt;10%</t>
+  </si>
+  <si>
+    <t>Gering (2):</t>
+  </si>
+  <si>
+    <t>10% - 30%</t>
+  </si>
+  <si>
+    <t>Mittel (3):</t>
+  </si>
+  <si>
+    <t>30% - 60%</t>
+  </si>
+  <si>
+    <t>Hoch (4):</t>
+  </si>
+  <si>
+    <t>60% - 90%</t>
+  </si>
+  <si>
+    <t>Sehr hoch (5):</t>
+  </si>
+  <si>
+    <t>&gt;90%</t>
+  </si>
+  <si>
     <r>
       <t>*</t>
     </r>
@@ -238,6 +417,21 @@
     </r>
   </si>
   <si>
+    <t>Geringfügige Auswirkung, leicht zu beheben (z.B. kleine Bugs)</t>
+  </si>
+  <si>
+    <t>Kleinere Verzögerungen (z.B Feature muss überarbeitet werden)</t>
+  </si>
+  <si>
+    <t>Deutliche Verzögerung, moderate Kosten, Beeinträchtigung der Qualität (z.B. Teilfunktionalität muss neu entwickelt werden)</t>
+  </si>
+  <si>
+    <t>Kritische Verzögerung, hohe Kosten, Projektziele gefährdet (z.B. Systemausfall, großer Datenverlust)</t>
+  </si>
+  <si>
+    <t>Projektabbruch, schwerwiegende finanzielle/reputative Schäden</t>
+  </si>
+  <si>
     <r>
       <t>*</t>
     </r>
@@ -264,223 +458,35 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Schadenshöhe *</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Risiko - Score *</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>Missverständnis der
- Anforderungen (kleine Anforderung)</t>
-  </si>
-  <si>
-    <t>Risikobereich (8)</t>
-  </si>
-  <si>
-    <t>Missverständnis der
- Anforderungen (mittlere Anforderung)</t>
-  </si>
-  <si>
-    <t>Risikobereich (9)</t>
-  </si>
-  <si>
-    <t>Missverständnis der
- Anforderungen (große Anforderung)</t>
-  </si>
-  <si>
-    <t>Mittel (4)</t>
-  </si>
-  <si>
-    <t>Änderungen an den
- Anforderungen nach Projektstart</t>
-  </si>
-  <si>
-    <t>Gefahrenbereich (12)</t>
-  </si>
-  <si>
-    <t>Mangelndes Engagement 
-des Teams / Entwickler</t>
-  </si>
-  <si>
-    <t>Fehlende Kompalibität 
-der Software zu Endgeräten</t>
-  </si>
-  <si>
-    <t>Akzeptanzbereich (4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Unzureichende oder 
-unrealistische Zeit- und Kostenplanung (P&amp;C)</t>
-  </si>
-  <si>
-    <t>Datenmodellierung in 
-MongoDB ist ineffizient oder fehlerhaft</t>
-  </si>
-  <si>
-    <t>Sicherheitslücken in der 
-Web-Applikation</t>
-  </si>
-  <si>
-    <t>Hoch (5)</t>
-  </si>
-  <si>
-    <t>Gefahrenbereich (15)</t>
-  </si>
-  <si>
-    <t>Ali, Sebo, Max, 
-Johannes</t>
-  </si>
-  <si>
-    <t>Johannes</t>
-  </si>
-  <si>
-    <t>Ali, Sebo</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurze Absprache vor 
-Entwicklung kleinerer 
-Anforderungen mit Fokus auf Verständnis </t>
-  </si>
-  <si>
-    <t>Genaue Ausdefinierungen 
-der mittleren Anforderungen mit Gespräch im Team und Kontrolle nach Fertigung</t>
-  </si>
-  <si>
-    <t>Klare Ziele zu Beginn jeder
- Entwicklungsphase. Klare Ausdefinierungen der einzelnen Elemente. Feedback zu Umgesetzten Features.</t>
-  </si>
-  <si>
-    <t>Klare Absprachen zu Beginn 
-der einzelnen Phasen und frühzeitige Funktionsanalyse</t>
-  </si>
-  <si>
-    <t>Gegenseitiges motivieren und 
-Fokussierung auf das Ziel</t>
-  </si>
-  <si>
-    <t>Vorab Recherge zu Soft- und 
-Hardware</t>
-  </si>
-  <si>
-    <t>Konsequentes zusammensetzten
-und Gespräche zur aktuellen Zeitplanung. Bei defizieten Rücksprache &amp; Korrektur.</t>
-  </si>
-  <si>
-    <t>Unit Tests durchführen und 
-Verschlüsselungen testen/ prüfen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johannes, lock in </t>
-  </si>
-  <si>
-    <t>in Bearbeitung</t>
-  </si>
-  <si>
-    <t>reduziert</t>
-  </si>
-  <si>
-    <t>eleminiert</t>
-  </si>
-  <si>
-    <t>offen</t>
-  </si>
-  <si>
-    <t>Schnelle Korrektur der Fehler, 
-oder entfernen der inkorrekten Umsetzung</t>
-  </si>
-  <si>
-    <t>Problembehandlung im Team.
-Kommunikation im Team und wenn nötig Anforderungen an Umsetzung anpassen</t>
-  </si>
-  <si>
-    <t>Anpassung der Anforderung in 
-Rücksprache mit dem Team oder Anpassung auf Feature</t>
-  </si>
-  <si>
-    <t>Admin Rechte entziehen und 
-Aufgaben auf das restliche Team auslagern</t>
-  </si>
-  <si>
-    <t>Endgeräte Anpassen/ Andere 
-Bibliotheken etc. verwenden</t>
-  </si>
-  <si>
-    <t>Mehr Zeit anfragen/ Geplante 
-Feature anpassen</t>
-  </si>
-  <si>
-    <t>Neu aufsetzen (falls möglich),
- sonst auf lokole Möglichkeiten ausweichen oder Datenmenge reduzieren</t>
-  </si>
-  <si>
-    <t>Nicht veröffentlichen/ Features 
-mit Sicherheitsriko entfernen/ Keine Sensiblen Daten Sammeln/ Auf Lücke hinweisen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt; Teilnahmequote an Meetings in %.
-&gt;  Erfüllungsquote zugesagter Tasks pro Sprint
-</t>
-  </si>
-  <si>
-    <t>&gt;Durchschnittliche 
-Auswirkung einer Änderung auf Zeit/Kosten</t>
-  </si>
-  <si>
-    <t>&gt;Anzahl offener 
-Rückfragen pro Anforderung.
-&gt;Anzahl Rework-Tickets pro Feature.</t>
-  </si>
-  <si>
-    <t>&gt; Anzahl gemeldeter Kompatibilitätsfehler
-&gt; Anzahl Darstellungs- oder Funktionsfehler pro Plattform</t>
-  </si>
-  <si>
-    <t>&gt; Anzahl verschobener Meilensteine
-&gt; Anteil unerledigter Aufgaben pro Sprint</t>
-  </si>
-  <si>
-    <t>&gt; Durchschnittliche Antwortzeit datenbankbasierter Abfragen
-&gt; Anzahl fehlerhafter oder inkonsistenter Datensätze</t>
-  </si>
-  <si>
-    <t>&gt; Anzahl gefundener Sicherheitslücken pro Testlauf
-&gt; Zeit bis zur Behebung sicherheitsrelevanter Schwachstellen</t>
+    <t>Akzeptanzbereich:</t>
+  </si>
+  <si>
+    <t>1 bis 4</t>
+  </si>
+  <si>
+    <t>Risikobereich:</t>
+  </si>
+  <si>
+    <t>5 bis 9</t>
+  </si>
+  <si>
+    <t>Gefahrenbereich:</t>
+  </si>
+  <si>
+    <t>10 bis 25</t>
+  </si>
+  <si>
+    <t>Aktualisierte Fassung</t>
+  </si>
+  <si>
+    <t>erledigt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,6 +537,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -552,7 +566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -577,6 +591,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -912,33 +929,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06591A36-7543-4BD1-BE9A-A11BCD87F7DD}">
-  <dimension ref="A1:K38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K54"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="6" width="29.109375" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" customWidth="1"/>
-    <col min="8" max="8" width="26.44140625" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="28.5546875" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="29.140625" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" customWidth="1"/>
+    <col min="8" max="8" width="26.42578125" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="23.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="16.149999999999999">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -946,465 +963,820 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
-        <v>7</v>
-      </c>
       <c r="J6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="72">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="J7" s="6" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K7" s="10">
         <v>46128</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="72">
       <c r="A8" s="5" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="K8" s="10">
         <v>46128</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="72">
       <c r="A9" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K9" s="10">
         <v>46128</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="43.15">
       <c r="A10" s="5" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="K10" s="10">
         <v>46128</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="86.45">
       <c r="A11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K11" s="10">
         <v>46128</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="72">
       <c r="A12" s="5" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="K12" s="10">
         <v>46128</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="57.6">
       <c r="A13" s="5" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="K13" s="10">
         <v>46128</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="86.45">
       <c r="A14" s="5" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="K14" s="10">
         <v>46128</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="86.45">
       <c r="A15" s="5" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="K15" s="10">
         <v>46128</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="16.149999999999999">
       <c r="A21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="16.149999999999999">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="16.149999999999999">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="29.25">
+      <c r="A43" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="15">
+      <c r="A45" t="s">
+        <v>2</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" t="s">
+        <v>6</v>
+      </c>
+      <c r="F45" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" t="s">
+        <v>11</v>
+      </c>
+      <c r="K45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="72.75">
+      <c r="A46" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="10">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="72.75">
+      <c r="A47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K47" s="10">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="72.75">
+      <c r="A48" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K48" s="10">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="43.5">
+      <c r="A49" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K49" s="10">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="87">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="G50" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K50" s="10">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="72.75">
+      <c r="A51" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K51" s="10">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="57.75">
+      <c r="A52" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="D52" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K52" s="10">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="101.25">
+      <c r="A53" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K53" s="10">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="87">
+      <c r="A54" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>44</v>
+      <c r="D54" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K54" s="10">
+        <v>46213</v>
       </c>
     </row>
   </sheetData>
